--- a/data/trans_orig/CAGE-Edad-trans_orig.xlsx
+++ b/data/trans_orig/CAGE-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2007</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>480599</t>
+          <t>480787</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>492033</t>
+          <t>491650</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>457290</t>
+          <t>457879</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>466539</t>
+          <t>466554</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>944281</t>
+          <t>943921</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>956382</t>
+          <t>956964</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>12182</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15241</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>722597</t>
+          <t>721773</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>732767</t>
+          <t>732775</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>615862</t>
+          <t>616791</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1342835</t>
+          <t>1343783</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1357031</t>
+          <t>1357077</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>883</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>627824</t>
+          <t>628205</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>636882</t>
+          <t>636901</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>684658</t>
+          <t>684893</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1315874</t>
+          <t>1315630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1326237</t>
+          <t>1325646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>517092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>519147</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>509758</t>
+          <t>509749</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1027860</t>
+          <t>1028917</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9371</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>373114</t>
+          <t>372107</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>383944</t>
+          <t>383951</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>397758</t>
+          <t>398808</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>773969</t>
+          <t>775454</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>787066</t>
+          <t>787146</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>290736</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>292583</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>341164</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>342934</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>633709</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>635517</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>205397</t>
+          <t>204018</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>331706</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>333908</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>537927</t>
+          <t>538726</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>16772</t>
+          <t>18583</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -4942,12 +4942,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>23439</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>31965</t>
+          <t>30430</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3237641</t>
+          <t>3238497</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3259498</t>
+          <t>3259529</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3361538</t>
+          <t>3360830</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3375477</t>
+          <t>3374871</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,47 +5105,47 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>99,87%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>6608034</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>6631537</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>99,89%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>6607397</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>6630932</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2012</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5520,12 +5520,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5633,12 +5633,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11654</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11981</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16147</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21916</t>
+          <t>21592</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>431808</t>
+          <t>431003</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>445977</t>
+          <t>445472</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>420808</t>
+          <t>420580</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>429205</t>
+          <t>429226</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>855937</t>
+          <t>856525</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>872716</t>
+          <t>872832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14763</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>13765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>662953</t>
+          <t>663676</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>678781</t>
+          <t>678921</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>608207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>610255</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1272990</t>
+          <t>1274625</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1289332</t>
+          <t>1289364</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>13070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12924</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11465</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11397</t>
+          <t>12030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>659672</t>
+          <t>658962</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>674159</t>
+          <t>674240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>708807</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>710850</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1371378</t>
+          <t>1370460</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1385415</t>
+          <t>1384909</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7262,12 +7262,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22129</t>
+          <t>20183</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19140</t>
+          <t>21645</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>591227</t>
+          <t>590937</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>609217</t>
+          <t>608476</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>614008</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>616199</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1207472</t>
+          <t>1205894</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1224633</t>
+          <t>1224469</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -7796,12 +7796,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12176</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>809</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>12617</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>415842</t>
+          <t>415602</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>428610</t>
+          <t>428607</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>442806</t>
+          <t>442752</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>863070</t>
+          <t>863634</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>875606</t>
+          <t>876224</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -8365,12 +8365,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12271</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13825</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -8704,12 +8704,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>297515</t>
+          <t>297487</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>308752</t>
+          <t>308769</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>352026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>353996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>649957</t>
+          <t>650034</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>662761</t>
+          <t>662754</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8984,12 +8984,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>11787</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11380</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>238708</t>
+          <t>238064</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>386852</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>388979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>627450</t>
+          <t>628741</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>16772</t>
+          <t>16376</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9553,42 +9553,42 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>8882</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>4175</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>16456</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
           <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>8882</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>4554</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>17087</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>13198</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>32783</t>
+          <t>32989</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>33640</t>
+          <t>35061</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -9729,12 +9729,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>24821</t>
+          <t>24424</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>51869</t>
+          <t>48962</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>28265</t>
+          <t>29203</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>56115</t>
+          <t>56191</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3340833</t>
+          <t>3342445</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3376500</t>
+          <t>3376774</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3546904</t>
+          <t>3546864</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3556323</t>
+          <t>3556320</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6893666</t>
+          <t>6895004</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6929953</t>
+          <t>6929706</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2016</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10307,12 +10307,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10322,12 +10322,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10425,7 +10425,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8152</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14697</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>405772</t>
+          <t>406863</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>417181</t>
+          <t>417514</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>387693</t>
+          <t>387603</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>394816</t>
+          <t>394821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>798011</t>
+          <t>799540</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>811085</t>
+          <t>811807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -10876,12 +10876,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10891,12 +10891,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -10989,12 +10989,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>10874</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19385</t>
+          <t>18591</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23086</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>566177</t>
+          <t>566821</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>582946</t>
+          <t>582362</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>552909</t>
+          <t>553767</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>561706</t>
+          <t>561702</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1124292</t>
+          <t>1124306</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1142176</t>
+          <t>1141985</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -11445,12 +11445,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11460,12 +11460,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11558,12 +11558,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11578,7 +11578,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>959</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11968</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13993</t>
+          <t>13447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>653438</t>
+          <t>653301</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>665376</t>
+          <t>665471</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>655281</t>
+          <t>655295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1312758</t>
+          <t>1312519</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1325730</t>
+          <t>1325804</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12177,12 +12177,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15775</t>
+          <t>15633</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18337</t>
+          <t>18377</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>626381</t>
+          <t>625628</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>641594</t>
+          <t>641556</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>640137</t>
+          <t>639855</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>647982</t>
+          <t>647976</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1271110</t>
+          <t>1271672</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1288196</t>
+          <t>1287410</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12633,12 +12633,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -12701,7 +12701,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12731,12 +12731,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12746,12 +12746,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14153</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12829,7 +12829,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19099</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12894,12 +12894,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -12922,12 +12922,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>461169</t>
+          <t>460749</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>474543</t>
+          <t>474532</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>486600</t>
+          <t>486239</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>952001</t>
+          <t>953742</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>969508</t>
+          <t>969149</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13007,12 +13007,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -13152,12 +13152,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13167,12 +13167,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13187,12 +13187,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13202,12 +13202,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13222,12 +13222,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13237,12 +13237,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13270,7 +13270,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13300,12 +13300,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13315,12 +13315,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13355,7 +13355,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -13378,12 +13378,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13393,12 +13393,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>329071</t>
+          <t>328874</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>371375</t>
+          <t>372332</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>705875</t>
+          <t>705180</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -13736,12 +13736,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -13771,12 +13771,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13834,12 +13834,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -13849,12 +13849,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -13884,12 +13884,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -13904,12 +13904,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13919,12 +13919,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13997,12 +13997,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>252451</t>
+          <t>252406</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -14095,12 +14095,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>397626</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>400169</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14110,12 +14110,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>652585</t>
+          <t>652595</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14310,7 +14310,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14345,7 +14345,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -14403,12 +14403,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>20954</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14418,12 +14418,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14458,7 +14458,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>22500</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14488,12 +14488,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -14516,12 +14516,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>23954</t>
+          <t>23565</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>49083</t>
+          <t>49213</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -14551,12 +14551,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24246</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14586,12 +14586,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>35340</t>
+          <t>33302</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>65528</t>
+          <t>62976</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14601,12 +14601,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -14629,12 +14629,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3328454</t>
+          <t>3328658</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3357958</t>
+          <t>3358339</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3516511</t>
+          <t>3517413</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3534797</t>
+          <t>3534672</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14679,12 +14679,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6853576</t>
+          <t>6855302</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6887541</t>
+          <t>6888494</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14714,12 +14714,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -14899,7 +14899,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2023</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -15094,12 +15094,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -15109,12 +15109,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>169</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -15164,12 +15164,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>161</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14154</t>
+          <t>13827</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -15179,12 +15179,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -15207,12 +15207,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -15222,12 +15222,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -15242,12 +15242,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -15257,12 +15257,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -15277,12 +15277,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -15292,12 +15292,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -15340,7 +15340,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -15355,12 +15355,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -15370,12 +15370,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -15395,7 +15395,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>860</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>169034</t>
+          <t>169085</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86019</t>
+          <t>87002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98909</t>
+          <t>98913</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -15483,7 +15483,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -15503,12 +15503,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>254834</t>
+          <t>255022</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>268511</t>
+          <t>268669</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -15518,12 +15518,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -15663,12 +15663,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -15678,12 +15678,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -15703,7 +15703,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -15781,7 +15781,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -15796,7 +15796,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -15811,12 +15811,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -15826,12 +15826,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -15889,12 +15889,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16868</t>
+          <t>16732</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -15904,12 +15904,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -15924,12 +15924,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -15939,12 +15939,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -15959,12 +15959,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14788</t>
+          <t>16583</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -15974,12 +15974,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -16002,12 +16002,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>211806</t>
+          <t>211645</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>227540</t>
+          <t>227802</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -16017,12 +16017,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>136236</t>
+          <t>136440</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -16072,12 +16072,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>353659</t>
+          <t>351247</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>367768</t>
+          <t>368060</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -16087,12 +16087,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -16237,7 +16237,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16302,12 +16302,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -16345,12 +16345,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -16365,7 +16365,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -16385,7 +16385,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -16415,12 +16415,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>998</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -16430,12 +16430,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -16463,7 +16463,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -16493,12 +16493,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -16508,12 +16508,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>844</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -16571,12 +16571,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>272230</t>
+          <t>270630</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>279968</t>
+          <t>279978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -16606,12 +16606,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>144491</t>
+          <t>144563</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>149652</t>
+          <t>149650</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -16621,7 +16621,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -16641,12 +16641,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>418686</t>
+          <t>419955</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428610</t>
+          <t>428767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -16656,12 +16656,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -16801,12 +16801,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6723</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -16836,12 +16836,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -16851,12 +16851,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -16871,12 +16871,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -16969,7 +16969,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -16984,12 +16984,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -17004,7 +17004,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -17032,7 +17032,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -17047,7 +17047,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -17082,7 +17082,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -17097,12 +17097,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>899</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -17140,12 +17140,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>327807</t>
+          <t>327244</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>337911</t>
+          <t>337823</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -17175,12 +17175,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>181934</t>
+          <t>181257</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>186859</t>
+          <t>186847</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -17190,12 +17190,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -17210,12 +17210,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>512284</t>
+          <t>512621</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>523420</t>
+          <t>523715</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -17225,12 +17225,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -17370,12 +17370,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -17385,12 +17385,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -17405,12 +17405,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -17440,12 +17440,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12569</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -17460,7 +17460,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -17483,12 +17483,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>821</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -17498,12 +17498,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -17553,12 +17553,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -17568,12 +17568,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -17596,12 +17596,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -17651,7 +17651,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -17666,12 +17666,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -17686,7 +17686,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -17709,12 +17709,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>243315</t>
+          <t>243352</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>256354</t>
+          <t>255772</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -17744,12 +17744,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>127496</t>
+          <t>127175</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>133497</t>
+          <t>133236</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -17759,12 +17759,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -17779,12 +17779,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>374689</t>
+          <t>375187</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>388048</t>
+          <t>388054</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -17939,12 +17939,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -17954,12 +17954,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -18009,12 +18009,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -18057,7 +18057,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>906</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -18087,12 +18087,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -18102,12 +18102,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -18127,7 +18127,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>865</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -18170,7 +18170,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -18185,7 +18185,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18200,12 +18200,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -18215,12 +18215,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -18240,7 +18240,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -18255,7 +18255,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -18278,12 +18278,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>180846</t>
+          <t>181088</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>187595</t>
+          <t>187482</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -18293,12 +18293,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -18313,7 +18313,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>275349</t>
+          <t>275260</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -18328,7 +18328,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -18348,12 +18348,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>456832</t>
+          <t>456981</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>467362</t>
+          <t>467370</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -18528,7 +18528,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -18578,12 +18578,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>410</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -18593,12 +18593,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -18656,12 +18656,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -18671,12 +18671,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -18769,12 +18769,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -18784,12 +18784,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -18847,12 +18847,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>93839</t>
+          <t>93718</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>99463</t>
+          <t>99341</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -18862,12 +18862,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -18882,7 +18882,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>24420</t>
+          <t>24575</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -18897,7 +18897,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -18917,12 +18917,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>120445</t>
+          <t>120658</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>125667</t>
+          <t>125660</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -18932,12 +18932,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -19077,12 +19077,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>19054</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -19112,12 +19112,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>18825</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -19127,12 +19127,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -19147,12 +19147,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>13162</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>31732</t>
+          <t>31088</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -19162,12 +19162,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -19190,12 +19190,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>18594</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19205,12 +19205,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19225,12 +19225,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>20698</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -19303,12 +19303,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>25471</t>
+          <t>23934</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19318,12 +19318,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19338,12 +19338,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>450</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -19353,12 +19353,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -19373,12 +19373,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>28032</t>
+          <t>26727</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -19388,12 +19388,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1524803</t>
+          <t>1523399</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1548782</t>
+          <t>1547632</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -19431,12 +19431,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -19451,12 +19451,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>994878</t>
+          <t>993489</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1011772</t>
+          <t>1011904</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -19466,12 +19466,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -19486,12 +19486,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2526989</t>
+          <t>2526518</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2556512</t>
+          <t>2558404</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -19501,12 +19501,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CAGE-Edad-trans_orig.xlsx
+++ b/data/trans_orig/CAGE-Edad-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>8944</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12456</t>
+          <t>13474</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>480787</t>
+          <t>480218</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>491650</t>
+          <t>491403</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>457879</t>
+          <t>457921</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>466554</t>
+          <t>466540</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>943921</t>
+          <t>944319</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>956964</t>
+          <t>957000</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>15424</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>721773</t>
+          <t>721870</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>732775</t>
+          <t>732958</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>616791</t>
+          <t>615792</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1343783</t>
+          <t>1342816</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1357077</t>
+          <t>1356659</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>882</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>628205</t>
+          <t>627103</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>636901</t>
+          <t>636743</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>684893</t>
+          <t>684659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1315630</t>
+          <t>1315657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1325646</t>
+          <t>1325686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>509749</t>
+          <t>508952</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1028917</t>
+          <t>1028920</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>915</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>928</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>372107</t>
+          <t>372281</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>383951</t>
+          <t>383864</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>398808</t>
+          <t>398528</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>775454</t>
+          <t>774309</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>787146</t>
+          <t>786952</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>204018</t>
+          <t>204799</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>538726</t>
+          <t>538724</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -4942,12 +4942,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>23415</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>30430</t>
+          <t>29432</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3238497</t>
+          <t>3238570</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3259529</t>
+          <t>3259691</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5075,77 +5075,77 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>3289</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>3369908</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>3360686</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3374565</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>6606768</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>6630767</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>3289</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>3369908</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>3360830</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>3374871</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>6608034</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>6631537</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -5633,12 +5633,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16729</t>
+          <t>16392</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21592</t>
+          <t>21621</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>431003</t>
+          <t>431024</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>445472</t>
+          <t>446057</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>420580</t>
+          <t>419710</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>429226</t>
+          <t>429217</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>856525</t>
+          <t>856774</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>872832</t>
+          <t>873278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>14703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>14584</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>663676</t>
+          <t>663939</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>678921</t>
+          <t>678838</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1274625</t>
+          <t>1272591</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1289364</t>
+          <t>1288577</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>13804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11628</t>
+          <t>11786</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12030</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>658962</t>
+          <t>659718</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>674240</t>
+          <t>674384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1370460</t>
+          <t>1370361</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1384909</t>
+          <t>1385436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21645</t>
+          <t>20978</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>590937</t>
+          <t>590034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>608476</t>
+          <t>608414</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1205894</t>
+          <t>1207286</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1224469</t>
+          <t>1224850</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14263</t>
+          <t>12811</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>819</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12617</t>
+          <t>13873</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>415602</t>
+          <t>416206</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>428607</t>
+          <t>428614</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>442752</t>
+          <t>442795</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>863634</t>
+          <t>863367</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>876224</t>
+          <t>875448</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12299</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>13002</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8676,12 +8676,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -8704,12 +8704,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>297487</t>
+          <t>296686</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>308769</t>
+          <t>307915</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>650034</t>
+          <t>650780</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>662754</t>
+          <t>661905</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11787</t>
+          <t>11114</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10089</t>
+          <t>11376</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>238064</t>
+          <t>238737</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>628741</t>
+          <t>627454</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>16010</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>16456</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>13198</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>32989</t>
+          <t>35988</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>35061</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -9729,12 +9729,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>25133</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>48962</t>
+          <t>50588</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>29203</t>
+          <t>28378</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>56191</t>
+          <t>56898</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3342445</t>
+          <t>3341906</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3376774</t>
+          <t>3377081</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3546864</t>
+          <t>3546084</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3556320</t>
+          <t>3556330</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6895004</t>
+          <t>6894514</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6929706</t>
+          <t>6929568</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>11149</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>938</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>406863</t>
+          <t>405973</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>417514</t>
+          <t>417398</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>387603</t>
+          <t>387606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>394821</t>
+          <t>394817</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>799540</t>
+          <t>798231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>811807</t>
+          <t>811256</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -10989,12 +10989,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18591</t>
+          <t>17781</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>9711</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>23103</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>566821</t>
+          <t>566349</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>582362</t>
+          <t>582201</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>553767</t>
+          <t>552953</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>561702</t>
+          <t>561688</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1124306</t>
+          <t>1123403</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1141985</t>
+          <t>1141995</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11573,12 +11573,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>939</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>653301</t>
+          <t>654303</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>665471</t>
+          <t>665276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>655295</t>
+          <t>655939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1312519</t>
+          <t>1312246</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1325804</t>
+          <t>1325561</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -12240,54 +12240,54 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>2245</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>15325</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
           <t>2224</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>15633</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>7845</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>2224</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>7749</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>18423</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>625628</t>
+          <t>627225</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>641556</t>
+          <t>641164</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>639855</t>
+          <t>639154</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1271672</t>
+          <t>1269801</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1287410</t>
+          <t>1287813</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -12701,7 +12701,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14905</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>17877</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12894,12 +12894,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -12922,12 +12922,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>460749</t>
+          <t>460528</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>474532</t>
+          <t>474496</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12937,12 +12937,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>486239</t>
+          <t>486140</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>953742</t>
+          <t>954564</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>969149</t>
+          <t>969564</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13007,12 +13007,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -13270,7 +13270,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13355,7 +13355,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>328874</t>
+          <t>329504</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>372332</t>
+          <t>372369</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>705180</t>
+          <t>704946</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -14060,7 +14060,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>252406</t>
+          <t>252087</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>652595</t>
+          <t>651880</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14310,7 +14310,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14345,7 +14345,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -14403,12 +14403,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>23513</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14418,12 +14418,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14458,7 +14458,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>22500</t>
+          <t>23572</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14488,12 +14488,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -14516,12 +14516,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>23565</t>
+          <t>23492</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>49213</t>
+          <t>47579</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14551,12 +14551,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>23733</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14566,12 +14566,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14586,12 +14586,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>33302</t>
+          <t>34164</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>62976</t>
+          <t>62887</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -14629,12 +14629,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3328658</t>
+          <t>3330290</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3358339</t>
+          <t>3358349</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3517413</t>
+          <t>3518342</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3534672</t>
+          <t>3535282</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14679,12 +14679,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6855302</t>
+          <t>6854957</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6888494</t>
+          <t>6887685</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14714,12 +14714,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -15124,32 +15124,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12080</t>
+          <t>15358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -15159,32 +15159,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13827</t>
+          <t>17750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -15315,7 +15315,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -15325,12 +15325,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -15340,7 +15340,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -15395,12 +15395,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -15428,27 +15428,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>169738</t>
+          <t>164590</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>169085</t>
+          <t>157472</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -15463,32 +15463,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95081</t>
+          <t>104817</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87002</t>
+          <t>95637</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98913</t>
+          <t>109308</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -15498,32 +15498,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>264819</t>
+          <t>269407</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>255022</t>
+          <t>257081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>268669</t>
+          <t>275052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -15541,17 +15541,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -15576,17 +15576,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>99082</t>
+          <t>110995</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99082</t>
+          <t>110995</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99082</t>
+          <t>110995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -15611,17 +15611,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>268985</t>
+          <t>277238</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>268985</t>
+          <t>277238</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>268985</t>
+          <t>277238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>861</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -15703,12 +15703,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>861</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -15738,12 +15738,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -15771,7 +15771,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -15781,12 +15781,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -15796,7 +15796,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -15851,12 +15851,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -15884,32 +15884,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>2291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -15954,32 +15954,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16583</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -15997,32 +15997,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>222840</t>
+          <t>241468</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>211645</t>
+          <t>231327</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>227802</t>
+          <t>246464</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -16032,27 +16032,27 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>139855</t>
+          <t>150647</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>136440</t>
+          <t>147237</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>151508</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -16067,32 +16067,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>362695</t>
+          <t>392115</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>351247</t>
+          <t>381847</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>368060</t>
+          <t>397451</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -16110,17 +16110,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -16145,17 +16145,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>151508</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>151508</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>151508</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -16180,17 +16180,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>370847</t>
+          <t>400972</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>370847</t>
+          <t>400972</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>370847</t>
+          <t>400972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -16237,12 +16237,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -16272,12 +16272,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16297,22 +16297,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>470</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -16340,32 +16340,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>455</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9291</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -16385,12 +16385,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -16410,32 +16410,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>10778</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -16463,12 +16463,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -16523,7 +16523,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -16533,12 +16533,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -16566,32 +16566,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>277509</t>
+          <t>305916</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>270630</t>
+          <t>299037</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>279978</t>
+          <t>309401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -16601,32 +16601,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>148138</t>
+          <t>167062</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>144563</t>
+          <t>163442</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>149650</t>
+          <t>168689</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -16636,32 +16636,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>425647</t>
+          <t>472976</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>419955</t>
+          <t>465358</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428767</t>
+          <t>477234</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -16679,17 +16679,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>281158</t>
+          <t>311643</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>281158</t>
+          <t>311643</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>281158</t>
+          <t>311643</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -16714,17 +16714,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>150090</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>150090</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>150090</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -16749,17 +16749,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>431248</t>
+          <t>480791</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>431248</t>
+          <t>480791</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>431248</t>
+          <t>480791</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -16796,32 +16796,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>810</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -16866,32 +16866,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>806</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -16909,7 +16909,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -16919,12 +16919,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -16944,7 +16944,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -16954,12 +16954,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -16969,7 +16969,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -16979,32 +16979,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>922</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -17032,12 +17032,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -17047,7 +17047,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -17057,7 +17057,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -17067,12 +17067,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -17082,7 +17082,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -17092,32 +17092,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>774</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -17135,32 +17135,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>334059</t>
+          <t>342849</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>327244</t>
+          <t>336298</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>337823</t>
+          <t>346816</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -17170,32 +17170,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>185368</t>
+          <t>204879</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>181257</t>
+          <t>201264</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>186847</t>
+          <t>206987</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -17205,32 +17205,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>519427</t>
+          <t>547728</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>512621</t>
+          <t>540159</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>523715</t>
+          <t>552235</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -17248,17 +17248,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>340160</t>
+          <t>349759</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>340160</t>
+          <t>349759</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>340160</t>
+          <t>349759</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -17283,17 +17283,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>187519</t>
+          <t>207698</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>187519</t>
+          <t>207698</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>187519</t>
+          <t>207698</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -17318,17 +17318,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>527679</t>
+          <t>557457</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>527679</t>
+          <t>557457</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>527679</t>
+          <t>557457</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -17365,32 +17365,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10776</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -17400,67 +17400,67 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>7276</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>3504</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>12609</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>1,7%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>7273</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3492</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>13258</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -17478,22 +17478,22 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>867</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -17503,7 +17503,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -17513,7 +17513,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>716</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -17523,12 +17523,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -17548,32 +17548,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -17591,32 +17591,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>8859</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -17626,7 +17626,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>689</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -17651,7 +17651,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -17661,32 +17661,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -17704,32 +17704,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>251136</t>
+          <t>267760</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>243352</t>
+          <t>260410</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>255772</t>
+          <t>272652</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -17739,32 +17739,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>131213</t>
+          <t>144145</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>127175</t>
+          <t>140121</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>133236</t>
+          <t>146297</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -17774,32 +17774,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>382348</t>
+          <t>411904</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>375187</t>
+          <t>404209</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>388054</t>
+          <t>417867</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -17817,17 +17817,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>262852</t>
+          <t>279361</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>262852</t>
+          <t>279361</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>262852</t>
+          <t>279361</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -17852,17 +17852,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -17887,17 +17887,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>397608</t>
+          <t>427318</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>397608</t>
+          <t>427318</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>397608</t>
+          <t>427318</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -17934,32 +17934,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>457</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -17979,12 +17979,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -18004,32 +18004,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -18047,7 +18047,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>874</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -18057,12 +18057,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>874</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -18127,12 +18127,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -18160,7 +18160,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -18170,12 +18170,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -18185,7 +18185,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18230,7 +18230,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -18240,12 +18240,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -18255,7 +18255,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -18273,32 +18273,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>185299</t>
+          <t>202216</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>181088</t>
+          <t>197630</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>187482</t>
+          <t>205128</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -18308,27 +18308,27 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>278356</t>
+          <t>78441</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>275260</t>
+          <t>77003</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>278806</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -18343,32 +18343,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>463654</t>
+          <t>280657</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>456981</t>
+          <t>275610</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>467370</t>
+          <t>283490</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -18386,17 +18386,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>189295</t>
+          <t>207092</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>189295</t>
+          <t>207092</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>189295</t>
+          <t>207092</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -18421,17 +18421,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>278806</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>278806</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>278806</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -18456,17 +18456,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>468100</t>
+          <t>285990</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>468100</t>
+          <t>285990</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>468100</t>
+          <t>285990</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -18513,12 +18513,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -18528,7 +18528,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -18538,7 +18538,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -18548,12 +18548,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -18573,32 +18573,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>426</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -18616,7 +18616,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>561</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -18626,12 +18626,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>561</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>533</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -18739,12 +18739,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>533</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -18809,12 +18809,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -18842,32 +18842,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>97652</t>
+          <t>107293</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>93718</t>
+          <t>103891</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>99341</t>
+          <t>109173</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -18877,27 +18877,27 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>26192</t>
+          <t>29689</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>24575</t>
+          <t>27875</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -18912,32 +18912,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>123844</t>
+          <t>136982</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>120658</t>
+          <t>133150</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>125660</t>
+          <t>138881</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -18955,17 +18955,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -18990,17 +18990,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -19025,17 +19025,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>126631</t>
+          <t>139861</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>126631</t>
+          <t>139861</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>126631</t>
+          <t>139861</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -19072,22 +19072,22 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -19107,32 +19107,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>22949</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -19142,32 +19142,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>16580</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>31088</t>
+          <t>37027</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -19185,32 +19185,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>18594</t>
+          <t>20414</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19220,32 +19220,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19255,32 +19255,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>22444</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -19298,32 +19298,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>23934</t>
+          <t>29136</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19333,32 +19333,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -19368,32 +19368,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>11276</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>26727</t>
+          <t>30020</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -19411,32 +19411,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1538231</t>
+          <t>1632092</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1523399</t>
+          <t>1617778</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1547632</t>
+          <t>1643478</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -19446,32 +19446,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1004202</t>
+          <t>879679</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>993489</t>
+          <t>867843</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1011904</t>
+          <t>886578</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -19481,32 +19481,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>2542434</t>
+          <t>2511770</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2526518</t>
+          <t>2495242</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2558404</t>
+          <t>2525557</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -19524,17 +19524,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -19559,17 +19559,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -19594,17 +19594,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
